--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.17802710669354</v>
+        <v>1.8164294048377</v>
       </c>
       <c r="D2" t="n">
-        <v>13.63799837369515</v>
+        <v>2.216174735725462</v>
       </c>
       <c r="E2" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.75404510421588</v>
+        <v>5.32253232943508</v>
       </c>
       <c r="D3" t="n">
-        <v>34.12715628995117</v>
+        <v>5.545662897117066</v>
       </c>
       <c r="E3" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F3" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.04580102870587</v>
+        <v>2.607442667164704</v>
       </c>
       <c r="D4" t="n">
-        <v>16.21000709222872</v>
+        <v>2.634126152487168</v>
       </c>
       <c r="E4" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F4" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.10442757471982</v>
+        <v>1.641969480891972</v>
       </c>
       <c r="D5" t="n">
-        <v>9.379356475379435</v>
+        <v>1.524145427249158</v>
       </c>
       <c r="E5" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F5" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.70052267978206</v>
+        <v>5.476334935464585</v>
       </c>
       <c r="D6" t="n">
-        <v>33.64290527980337</v>
+        <v>5.466972107968048</v>
       </c>
       <c r="E6" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F6" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.06419703198861</v>
+        <v>4.072932017698149</v>
       </c>
       <c r="D7" t="n">
-        <v>23.17733439476369</v>
+        <v>3.7663168391491</v>
       </c>
       <c r="E7" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F7" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.05964197435405</v>
+        <v>5.047191820832534</v>
       </c>
       <c r="D8" t="n">
-        <v>28.4810843998378</v>
+        <v>4.628176214973643</v>
       </c>
       <c r="E8" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F8" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.21788584193792</v>
+        <v>3.935406449314913</v>
       </c>
       <c r="D9" t="n">
-        <v>24.30467496372586</v>
+        <v>3.949509681605453</v>
       </c>
       <c r="E9" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F9" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>5.950652786230921</v>
+        <v>0.9669810777625247</v>
       </c>
       <c r="D10" t="n">
-        <v>6.241682071039249</v>
+        <v>1.014273336543878</v>
       </c>
       <c r="E10" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F10" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.45056714393832</v>
+        <v>6.085717160889978</v>
       </c>
       <c r="D11" t="n">
-        <v>37.23204627285871</v>
+        <v>6.050207519339541</v>
       </c>
       <c r="E11" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.12358478380141</v>
+        <v>2.62008252736773</v>
       </c>
       <c r="D12" t="n">
-        <v>15.96679811434621</v>
+        <v>2.59460469358126</v>
       </c>
       <c r="E12" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F12" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.82397491991088</v>
+        <v>3.383895924485518</v>
       </c>
       <c r="D13" t="n">
-        <v>21.10356315331014</v>
+        <v>3.429329012412898</v>
       </c>
       <c r="E13" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.3335240337454</v>
+        <v>5.579197655483627</v>
       </c>
       <c r="D14" t="n">
-        <v>34.60477589771928</v>
+        <v>5.623276083379383</v>
       </c>
       <c r="E14" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F14" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.47472353508573</v>
+        <v>6.252142574451431</v>
       </c>
       <c r="D15" t="n">
-        <v>38.4153652230039</v>
+        <v>6.242496848738134</v>
       </c>
       <c r="E15" t="n">
-        <v>10.47962291552844</v>
+        <v>1.702938723773371</v>
       </c>
       <c r="F15" t="n">
-        <v>10.2880786242119</v>
+        <v>1.671812776434434</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
